--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -1,20 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E258135-79E3-4BA9-83E3-8218C57CD072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="circuit_scorecard" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+  <si>
+    <t>Court Below</t>
+  </si>
+  <si>
+    <t># of Cases</t>
+  </si>
+  <si>
+    <t>% of Cases</t>
+  </si>
+  <si>
+    <t># Decided</t>
+  </si>
+  <si>
+    <t># Affirm</t>
+  </si>
+  <si>
+    <t># Reversed</t>
+  </si>
+  <si>
+    <t>% Affirmed</t>
+  </si>
+  <si>
+    <t>% Reversed</t>
+  </si>
+  <si>
+    <t>CA1</t>
+  </si>
+  <si>
+    <t>CA2</t>
+  </si>
+  <si>
+    <t>CA3</t>
+  </si>
+  <si>
+    <t>CA4</t>
+  </si>
+  <si>
+    <t>CA5</t>
+  </si>
+  <si>
+    <t>CA6</t>
+  </si>
+  <si>
+    <t>CA7</t>
+  </si>
+  <si>
+    <t>CA8</t>
+  </si>
+  <si>
+    <t>CA9</t>
+  </si>
+  <si>
+    <t>CA10</t>
+  </si>
+  <si>
+    <t>CA11</t>
+  </si>
+  <si>
+    <t>CADC</t>
+  </si>
+  <si>
+    <t>CAFED</t>
+  </si>
+  <si>
+    <t>State Court</t>
+  </si>
+  <si>
+    <t>District Court</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -50,6 +131,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -331,11 +421,428 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H2" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>0.5</v>
+      </c>
+      <c r="H3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>0.03</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H4" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>0.121</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>0.182</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H7" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>0.03</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0.03</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0.5</v>
+      </c>
+      <c r="H12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="H13">
+        <v>0.66700000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0.5</v>
+      </c>
+      <c r="H14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H16" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -1,101 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E258135-79E3-4BA9-83E3-8218C57CD072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="circuit_scorecard" sheetId="1" r:id="rId1"/>
+    <sheet name="circuit_scorecard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
-    <t>Court Below</t>
-  </si>
-  <si>
-    <t># of Cases</t>
-  </si>
-  <si>
-    <t>% of Cases</t>
-  </si>
-  <si>
-    <t># Decided</t>
-  </si>
-  <si>
-    <t># Affirm</t>
-  </si>
-  <si>
-    <t># Reversed</t>
-  </si>
-  <si>
-    <t>% Affirmed</t>
-  </si>
-  <si>
-    <t>% Reversed</t>
-  </si>
-  <si>
-    <t>CA1</t>
-  </si>
-  <si>
-    <t>CA2</t>
-  </si>
-  <si>
-    <t>CA3</t>
-  </si>
-  <si>
-    <t>CA4</t>
-  </si>
-  <si>
-    <t>CA5</t>
-  </si>
-  <si>
-    <t>CA6</t>
-  </si>
-  <si>
-    <t>CA7</t>
-  </si>
-  <si>
-    <t>CA8</t>
-  </si>
-  <si>
-    <t>CA9</t>
-  </si>
-  <si>
-    <t>CA10</t>
-  </si>
-  <si>
-    <t>CA11</t>
-  </si>
-  <si>
-    <t>CADC</t>
-  </si>
-  <si>
-    <t>CAFED</t>
-  </si>
-  <si>
-    <t>State Court</t>
-  </si>
-  <si>
-    <t>District Court</t>
+    <t xml:space="preserve">Court Below</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># of Cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of Cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Decided</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Affirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Reversed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Affirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Reversed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">District Court</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -131,15 +124,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -421,11 +405,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,23 +435,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="e">
@@ -477,49 +461,49 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="D3">
+      <c r="C3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D3" t="n">
         <v>4</v>
       </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.5</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.03</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="e">
@@ -529,75 +513,75 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>8</v>
       </c>
-      <c r="C5">
-        <v>0.121</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C5" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>0.182</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C6" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C7">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="C7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="e">
@@ -607,242 +591,266 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
         <v>0.03</v>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.5</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.03</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>6</v>
       </c>
-      <c r="C10">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="C11">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="C12">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
+      <c r="C12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.5</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>5</v>
       </c>
-      <c r="C13">
-        <v>7.5999999999999998E-2</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>0.33300000000000002</v>
-      </c>
-      <c r="H13">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>4</v>
       </c>
-      <c r="C15">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="e">
         <v>#NUM!</v>
       </c>
       <c r="H16" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H17" t="e">
         <v>#NUM!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -498,19 +498,19 @@
         <v>0.03</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H4" t="e">
-        <v>#NUM!</v>
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -544,10 +544,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.179</v>
+        <v>0.194</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -732,19 +732,19 @@
         <v>0.075</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -784,19 +784,19 @@
         <v>0.06</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="16">
@@ -822,30 +822,6 @@
         <v>#NUM!</v>
       </c>
       <c r="H16" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17"/>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H17" t="e">
         <v>#NUM!</v>
       </c>
     </row>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,24 +41,57 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
+    <t xml:space="preserve">1.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
+    <t xml:space="preserve">9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
+    <t xml:space="preserve">3%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
+    <t xml:space="preserve">11.9%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA5</t>
   </si>
   <si>
+    <t xml:space="preserve">19.4%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA6</t>
   </si>
   <si>
+    <t xml:space="preserve">6%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA7</t>
   </si>
   <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA8</t>
   </si>
   <si>
@@ -74,13 +107,28 @@
     <t xml:space="preserve">CADC</t>
   </si>
   <si>
+    <t xml:space="preserve">7.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAFED</t>
   </si>
   <si>
+    <t xml:space="preserve">4.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">State Court</t>
   </si>
   <si>
+    <t xml:space="preserve">75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25%</t>
+  </si>
+  <si>
     <t xml:space="preserve">District Court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
   </si>
 </sst>
 </file>
@@ -442,86 +490,86 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.015</v>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H2" t="e">
-        <v>#NUM!</v>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.09</v>
+      <c r="C3" t="s">
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5</v>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B5" t="n">
         <v>8</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.119</v>
+      <c r="C5" t="s">
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -532,22 +580,22 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.194</v>
+      <c r="C6" t="s">
+        <v>21</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -558,48 +606,48 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.06</v>
+      <c r="C7" t="s">
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H7" t="e">
-        <v>#NUM!</v>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.03</v>
+      <c r="C8" t="s">
+        <v>17</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -610,22 +658,22 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5</v>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.03</v>
+      <c r="C9" t="s">
+        <v>17</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -636,48 +684,48 @@
       <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.09</v>
+      <c r="C10" t="s">
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.06</v>
+      <c r="C11" t="s">
+        <v>23</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -688,22 +736,22 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.06</v>
+      <c r="C12" t="s">
+        <v>23</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -714,22 +762,22 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5</v>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.075</v>
+      <c r="C13" t="s">
+        <v>31</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -740,22 +788,22 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5</v>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.045</v>
+      <c r="C14" t="s">
+        <v>33</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -766,48 +814,48 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5</v>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.06</v>
+      <c r="C15" t="s">
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.333</v>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>0.045</v>
+      <c r="C16" t="s">
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -818,11 +866,11 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H16" t="e">
-        <v>#NUM!</v>
+      <c r="G16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -68,6 +68,9 @@
     <t xml:space="preserve">3%</t>
   </si>
   <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
@@ -80,6 +83,12 @@
     <t xml:space="preserve">19.4%</t>
   </si>
   <si>
+    <t xml:space="preserve">75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA6</t>
   </si>
   <si>
@@ -89,9 +98,6 @@
     <t xml:space="preserve">CA7</t>
   </si>
   <si>
-    <t xml:space="preserve">50%</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA8</t>
   </si>
   <si>
@@ -104,6 +110,12 @@
     <t xml:space="preserve">CA11</t>
   </si>
   <si>
+    <t xml:space="preserve">66.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CADC</t>
   </si>
   <si>
@@ -117,12 +129,6 @@
   </si>
   <si>
     <t xml:space="preserve">State Court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25%</t>
   </si>
   <si>
     <t xml:space="preserve">District Court</t>
@@ -546,36 +552,36 @@
         <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -589,39 +595,39 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -641,7 +647,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -659,15 +665,15 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -676,24 +682,24 @@
         <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
@@ -719,13 +725,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -745,39 +751,39 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
@@ -789,73 +795,73 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="H14" t="s">
         <v>33</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
         <v>23</v>
       </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>35</v>
-      </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -867,10 +873,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -56,79 +56,85 @@
     <t xml:space="preserve">9%</t>
   </si>
   <si>
+    <t xml:space="preserve">66.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5%</t>
+  </si>
+  <si>
     <t xml:space="preserve">60%</t>
   </si>
   <si>
     <t xml:space="preserve">40%</t>
   </si>
   <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4%</t>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Court</t>
   </si>
   <si>
     <t xml:space="preserve">75%</t>
   </si>
   <si>
     <t xml:space="preserve">25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAFED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State Court</t>
   </si>
   <si>
     <t xml:space="preserve">District Court</t>
@@ -526,10 +532,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -604,13 +610,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -630,19 +636,19 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -708,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -734,10 +740,10 @@
         <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -760,45 +766,45 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -821,10 +827,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -847,15 +853,15 @@
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
@@ -873,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,106 +41,88 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5%</t>
+    <t xml:space="preserve">2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
   </si>
   <si>
     <t xml:space="preserve">100%</t>
   </si>
   <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">9%</t>
+    <t xml:space="preserve">9.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3%</t>
   </si>
   <si>
     <t xml:space="preserve">66.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAFED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State Court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">District Court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA</t>
   </si>
 </sst>
 </file>
@@ -509,10 +491,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -526,19 +508,19 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -578,7 +560,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -587,10 +569,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -604,7 +586,7 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -613,10 +595,10 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -633,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -653,7 +635,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -679,7 +661,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -705,22 +687,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>3</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
       </c>
       <c r="G10" t="s">
         <v>10</v>
@@ -734,19 +716,19 @@
         <v>30</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -763,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -789,100 +771,48 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8%</t>
+    <t xml:space="preserve">10%</t>
   </si>
   <si>
     <t xml:space="preserve">40%</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9%</t>
+    <t xml:space="preserve">4%</t>
   </si>
   <si>
     <t xml:space="preserve">50%</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8%</t>
+    <t xml:space="preserve">8%</t>
   </si>
   <si>
     <t xml:space="preserve">CA5</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7%</t>
+    <t xml:space="preserve">14%</t>
   </si>
   <si>
     <t xml:space="preserve">28.6%</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">CA9</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8%</t>
+    <t xml:space="preserve">12%</t>
   </si>
   <si>
     <t xml:space="preserve">CA10</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">CAFED</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9%</t>
+    <t xml:space="preserve">6%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -586,7 +586,7 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">2%</t>
+    <t xml:space="preserve">1.8%</t>
   </si>
   <si>
     <t xml:space="preserve">0%</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">10%</t>
+    <t xml:space="preserve">9.1%</t>
   </si>
   <si>
     <t xml:space="preserve">40%</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">4%</t>
+    <t xml:space="preserve">3.6%</t>
   </si>
   <si>
     <t xml:space="preserve">50%</t>
@@ -74,24 +74,27 @@
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
-    <t xml:space="preserve">8%</t>
+    <t xml:space="preserve">10.9%</t>
   </si>
   <si>
     <t xml:space="preserve">CA5</t>
   </si>
   <si>
-    <t xml:space="preserve">14%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4%</t>
+    <t xml:space="preserve">18.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80%</t>
   </si>
   <si>
     <t xml:space="preserve">CA6</t>
   </si>
   <si>
+    <t xml:space="preserve">7.3%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA7</t>
   </si>
   <si>
@@ -101,9 +104,6 @@
     <t xml:space="preserve">CA9</t>
   </si>
   <si>
-    <t xml:space="preserve">12%</t>
-  </si>
-  <si>
     <t xml:space="preserve">CA10</t>
   </si>
   <si>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">CAFED</t>
   </si>
   <si>
-    <t xml:space="preserve">6%</t>
+    <t xml:space="preserve">5.5%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -560,19 +560,19 @@
         <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -586,19 +586,19 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -615,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -635,7 +635,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="n">
         <v>2</v>
@@ -687,13 +687,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -745,7 +745,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/circuit_scorecard.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">Court Below</t>
   </si>
@@ -41,7 +41,7 @@
     <t xml:space="preserve">CA1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8%</t>
+    <t xml:space="preserve">1.7%</t>
   </si>
   <si>
     <t xml:space="preserve">0%</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">CA2</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1%</t>
+    <t xml:space="preserve">8.3%</t>
   </si>
   <si>
     <t xml:space="preserve">40%</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">CA3</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6%</t>
+    <t xml:space="preserve">3.3%</t>
   </si>
   <si>
     <t xml:space="preserve">50%</t>
@@ -74,25 +74,25 @@
     <t xml:space="preserve">CA4</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9%</t>
+    <t xml:space="preserve">13.3%</t>
   </si>
   <si>
     <t xml:space="preserve">CA5</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80%</t>
+    <t xml:space="preserve">21.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9%</t>
   </si>
   <si>
     <t xml:space="preserve">CA6</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3%</t>
+    <t xml:space="preserve">6.7%</t>
   </si>
   <si>
     <t xml:space="preserve">CA7</t>
@@ -104,6 +104,9 @@
     <t xml:space="preserve">CA9</t>
   </si>
   <si>
+    <t xml:space="preserve">10%</t>
+  </si>
+  <si>
     <t xml:space="preserve">CA10</t>
   </si>
   <si>
@@ -116,7 +119,7 @@
     <t xml:space="preserve">CAFED</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5%</t>
+    <t xml:space="preserve">5%</t>
   </si>
   <si>
     <t xml:space="preserve">33.3%</t>
@@ -560,19 +563,19 @@
         <v>19</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -586,19 +589,19 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
         <v>10</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -693,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -713,7 +716,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="n">
         <v>5</v>
@@ -739,7 +742,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
@@ -765,7 +768,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" t="n">
         <v>5</v>
@@ -791,13 +794,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -809,10 +812,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
